--- a/artfynd/A 2028-2025 artfynd.xlsx
+++ b/artfynd/A 2028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4958,6 +4958,112 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122758265</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56687</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Dalvadisoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>673771</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7399563</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Hannu Rimpisalo</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin, Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2028-2025 artfynd.xlsx
+++ b/artfynd/A 2028-2025 artfynd.xlsx
@@ -4960,7 +4960,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122761565</v>
+        <v>122758265</v>
       </c>
       <c r="B44" t="n">
         <v>56688</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Brandt, Jenny Hjelm Córdoba, Elin Götmark</t>
+          <t>Cecilia Lundin, Linda Nordström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 2028-2025 artfynd.xlsx
+++ b/artfynd/A 2028-2025 artfynd.xlsx
@@ -4960,7 +4960,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122758265</v>
+        <v>122761565</v>
       </c>
       <c r="B44" t="n">
         <v>56688</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Lundin, Linda Nordström</t>
+          <t>Maria Brandt, Jenny Hjelm Córdoba, Elin Götmark</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 2028-2025 artfynd.xlsx
+++ b/artfynd/A 2028-2025 artfynd.xlsx
@@ -4960,10 +4960,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122758265</v>
+        <v>122761565</v>
       </c>
       <c r="B44" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Lundin, Linda Nordström</t>
+          <t>Maria Brandt, Jenny Hjelm Córdoba, Elin Götmark</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 2028-2025 artfynd.xlsx
+++ b/artfynd/A 2028-2025 artfynd.xlsx
@@ -4960,7 +4960,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122761565</v>
+        <v>122758265</v>
       </c>
       <c r="B44" t="n">
         <v>56691</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Brandt, Jenny Hjelm Córdoba, Elin Götmark</t>
+          <t>Cecilia Lundin, Linda Nordström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 2028-2025 artfynd.xlsx
+++ b/artfynd/A 2028-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118195911</v>
+        <v>119318689</v>
       </c>
       <c r="B2" t="n">
-        <v>82263</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>674054</v>
+        <v>673709</v>
       </c>
       <c r="R2" t="n">
-        <v>7399430</v>
+        <v>7399258</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118195898</v>
+        <v>119318690</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674062</v>
+        <v>673913</v>
       </c>
       <c r="R3" t="n">
-        <v>7399467</v>
+        <v>7399368</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,65 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118195886</v>
+        <v>119318692</v>
       </c>
       <c r="B4" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673882</v>
+        <v>674027</v>
       </c>
       <c r="R4" t="n">
-        <v>7399388</v>
+        <v>7399307</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118195899</v>
+        <v>119318693</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>673846</v>
+        <v>673651</v>
       </c>
       <c r="R5" t="n">
-        <v>7399514</v>
+        <v>7399681</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,49 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118195902</v>
+        <v>118195905</v>
       </c>
       <c r="B6" t="n">
-        <v>96807</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>673993</v>
+        <v>673711</v>
       </c>
       <c r="R6" t="n">
-        <v>7399327</v>
+        <v>7399249</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1188,12 +1163,7 @@
         <v>118195906</v>
       </c>
       <c r="B7" t="n">
-        <v>78566</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118195887</v>
+        <v>118195908</v>
       </c>
       <c r="B8" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>673918</v>
+        <v>673911</v>
       </c>
       <c r="R8" t="n">
-        <v>7399322</v>
+        <v>7399559</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118195888</v>
+        <v>118195909</v>
       </c>
       <c r="B9" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673942</v>
+        <v>673786</v>
       </c>
       <c r="R9" t="n">
-        <v>7399349</v>
+        <v>7399609</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,53 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118195885</v>
+        <v>119318654</v>
       </c>
       <c r="B10" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673607</v>
+        <v>673478</v>
       </c>
       <c r="R10" t="n">
-        <v>7399449</v>
+        <v>7399658</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,65 +1536,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118195914</v>
+        <v>119318656</v>
       </c>
       <c r="B11" t="n">
-        <v>79600</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>674040</v>
+        <v>674028</v>
       </c>
       <c r="R11" t="n">
-        <v>7399480</v>
+        <v>7399301</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,27 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118195905</v>
+        <v>119318657</v>
       </c>
       <c r="B12" t="n">
-        <v>78566</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,17 +1676,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673711</v>
+        <v>674059</v>
       </c>
       <c r="R12" t="n">
-        <v>7399249</v>
+        <v>7399464</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,27 +1730,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118195909</v>
+        <v>119318658</v>
       </c>
       <c r="B13" t="n">
-        <v>78566</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,17 +1773,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673786</v>
+        <v>674055</v>
       </c>
       <c r="R13" t="n">
-        <v>7399609</v>
+        <v>7399452</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,65 +1827,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118195910</v>
+        <v>119318660</v>
       </c>
       <c r="B14" t="n">
-        <v>90654</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>673758</v>
+        <v>673977</v>
       </c>
       <c r="R14" t="n">
-        <v>7399311</v>
+        <v>7399707</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,27 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118195908</v>
+        <v>119318661</v>
       </c>
       <c r="B15" t="n">
-        <v>78566</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,17 +1967,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dalvadisoajvve, Lu lm</t>
+          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>673911</v>
+        <v>673907</v>
       </c>
       <c r="R15" t="n">
-        <v>7399559</v>
+        <v>7399552</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,27 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119318654</v>
+        <v>119318662</v>
       </c>
       <c r="B16" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>673478</v>
+        <v>673912</v>
       </c>
       <c r="R16" t="n">
-        <v>7399658</v>
+        <v>7399527</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,12 +2133,7 @@
         <v>119318663</v>
       </c>
       <c r="B17" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,12 +2230,7 @@
         <v>119318664</v>
       </c>
       <c r="B18" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119318675</v>
+        <v>119318665</v>
       </c>
       <c r="B19" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674055</v>
+        <v>673772</v>
       </c>
       <c r="R19" t="n">
-        <v>7399447</v>
+        <v>7399634</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119318657</v>
+        <v>119318666</v>
       </c>
       <c r="B20" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2551,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674059</v>
+        <v>673758</v>
       </c>
       <c r="R20" t="n">
-        <v>7399464</v>
+        <v>7399669</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119318670</v>
+        <v>119318667</v>
       </c>
       <c r="B21" t="n">
-        <v>90712</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>673756</v>
+        <v>673749</v>
       </c>
       <c r="R21" t="n">
-        <v>7399315</v>
+        <v>7399656</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119318690</v>
+        <v>118195911</v>
       </c>
       <c r="B22" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,37 +2626,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>673913</v>
+        <v>674054</v>
       </c>
       <c r="R22" t="n">
-        <v>7399368</v>
+        <v>7399430</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2805,27 +2700,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119318679</v>
+        <v>119318674</v>
       </c>
       <c r="B23" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>673768</v>
+        <v>674056</v>
       </c>
       <c r="R23" t="n">
-        <v>7399662</v>
+        <v>7399467</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,37 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119318601</v>
+        <v>119318675</v>
       </c>
       <c r="B24" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>673707</v>
+        <v>674055</v>
       </c>
       <c r="R24" t="n">
-        <v>7399259</v>
+        <v>7399447</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,37 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119318703</v>
+        <v>119318678</v>
       </c>
       <c r="B25" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>674053</v>
+        <v>673844</v>
       </c>
       <c r="R25" t="n">
-        <v>7399454</v>
+        <v>7399513</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,15 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119318661</v>
+        <v>119318679</v>
       </c>
       <c r="B26" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>673907</v>
+        <v>673768</v>
       </c>
       <c r="R26" t="n">
-        <v>7399552</v>
+        <v>7399662</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,15 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119318666</v>
+        <v>119318680</v>
       </c>
       <c r="B27" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3268,7 +3138,7 @@
         <v>673758</v>
       </c>
       <c r="R27" t="n">
-        <v>7399669</v>
+        <v>7399670</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,53 +3197,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119318680</v>
+        <v>118195910</v>
       </c>
       <c r="B28" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
         <v>673758</v>
       </c>
       <c r="R28" t="n">
-        <v>7399670</v>
+        <v>7399311</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3417,49 +3282,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119318607</v>
+        <v>119318670</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>674010</v>
+        <v>673756</v>
       </c>
       <c r="R29" t="n">
-        <v>7399325</v>
+        <v>7399315</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,15 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119318634</v>
+        <v>119318643</v>
       </c>
       <c r="B30" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>673850</v>
+        <v>673598</v>
       </c>
       <c r="R30" t="n">
-        <v>7399521</v>
+        <v>7399422</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,6 +3470,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3633,37 +3489,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119318704</v>
+        <v>119318634</v>
       </c>
       <c r="B31" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3524,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>673764</v>
+        <v>673850</v>
       </c>
       <c r="R31" t="n">
-        <v>7399635</v>
+        <v>7399521</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,15 +3586,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119318674</v>
+        <v>118195904</v>
       </c>
       <c r="B32" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3751,37 +3597,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>674056</v>
+        <v>673481</v>
       </c>
       <c r="R32" t="n">
-        <v>7399467</v>
+        <v>7399700</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3825,12 +3671,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3840,12 +3686,7 @@
         <v>119318650</v>
       </c>
       <c r="B33" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3942,12 +3783,7 @@
         <v>119318651</v>
       </c>
       <c r="B34" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4041,53 +3877,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119318599</v>
+        <v>118195914</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>673493</v>
+        <v>674040</v>
       </c>
       <c r="R35" t="n">
-        <v>7399617</v>
+        <v>7399480</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4131,65 +3962,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119318662</v>
+        <v>118195898</v>
       </c>
       <c r="B36" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>673912</v>
+        <v>674062</v>
       </c>
       <c r="R36" t="n">
-        <v>7399527</v>
+        <v>7399467</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4233,65 +4059,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119318689</v>
+        <v>118195899</v>
       </c>
       <c r="B37" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>673709</v>
+        <v>673846</v>
       </c>
       <c r="R37" t="n">
-        <v>7399258</v>
+        <v>7399514</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4335,27 +4156,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119318665</v>
+        <v>119318598</v>
       </c>
       <c r="B38" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4363,21 +4179,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4203,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>673772</v>
+        <v>673660</v>
       </c>
       <c r="R38" t="n">
-        <v>7399634</v>
+        <v>7399695</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,15 +4265,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119318658</v>
+        <v>119318599</v>
       </c>
       <c r="B39" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4465,21 +4276,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4300,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674055</v>
+        <v>673493</v>
       </c>
       <c r="R39" t="n">
-        <v>7399452</v>
+        <v>7399617</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,15 +4362,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119318602</v>
+        <v>122758265</v>
       </c>
       <c r="B40" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4585,19 +4391,23 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>673779</v>
+        <v>673771</v>
       </c>
       <c r="R40" t="n">
-        <v>7399341</v>
+        <v>7399563</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4641,49 +4451,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Hannu Rimpisalo</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin, Linda Nordström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119318643</v>
+        <v>119318703</v>
       </c>
       <c r="B41" t="n">
-        <v>92030</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>673598</v>
+        <v>674053</v>
       </c>
       <c r="R41" t="n">
-        <v>7399422</v>
+        <v>7399454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4737,7 +4542,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4756,37 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119318667</v>
+        <v>119318704</v>
       </c>
       <c r="B42" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>864</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4796,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>673749</v>
+        <v>673764</v>
       </c>
       <c r="R42" t="n">
-        <v>7399656</v>
+        <v>7399635</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4858,15 +4657,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119318678</v>
+        <v>118195903</v>
       </c>
       <c r="B43" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,37 +4668,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Dalvvadisoajve och Njárggavárre, Lu lm</t>
+          <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>673844</v>
+        <v>673937</v>
       </c>
       <c r="R43" t="n">
-        <v>7399513</v>
+        <v>7399618</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4948,27 +4742,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122758265</v>
+        <v>118195902</v>
       </c>
       <c r="B44" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4976,41 +4765,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Dalvadisoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>673771</v>
+        <v>673993</v>
       </c>
       <c r="R44" t="n">
-        <v>7399563</v>
+        <v>7399327</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5054,12 +4839,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Hannu Rimpisalo</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Lundin, Linda Nordström</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 2028-2025 artfynd.xlsx
+++ b/artfynd/A 2028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318689</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318690</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318692</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318693</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195905</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195906</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195908</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195909</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318654</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318656</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318657</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318658</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318660</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318661</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318662</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318663</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318664</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318665</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318666</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318667</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195911</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318674</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318675</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318678</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318679</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318680</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195910</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318670</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3486,6 +3631,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318643</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3583,6 +3733,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318634</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3680,6 +3835,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195904</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3777,6 +3937,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318650</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3874,6 +4039,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318651</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3971,6 +4141,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195914</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4068,6 +4243,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195898</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4165,6 +4345,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195899</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4262,6 +4447,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318598</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4359,6 +4549,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318599</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4460,6 +4655,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122758265</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4557,6 +4757,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318703</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4654,6 +4859,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119318704</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4751,6 +4961,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195903</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4848,8 +5063,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118195902</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>